--- a/src/test/resources/testdata/CheckoutData.xlsx
+++ b/src/test/resources/testdata/CheckoutData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OnlyInterviewQA\selenium-pom-testng-cicd\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE9F9200-0C09-477F-8ED8-043400AF7DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFF2A2C-99BB-4808-94C9-EB23C8880237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F120BD0C-6C12-4E10-8BB0-81F5E90C5E7A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>FirstName</t>
   </si>
@@ -52,21 +52,6 @@
   </si>
   <si>
     <t>Doe</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>Rahul</t>
-  </si>
-  <si>
-    <t>Sharma</t>
-  </si>
-  <si>
-    <t>(blank)</t>
   </si>
   <si>
     <t>A</t>
@@ -453,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA1DB71-F0E9-4C61-BA86-3C45F1445385}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.7265625" customWidth="1"/>
@@ -496,65 +481,9 @@
         <v>7</v>
       </c>
       <c r="C3" s="2">
-        <v>10001</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2">
-        <v>110001</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2">
-        <v>560001</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
-        <v>560001</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2">
-        <v>123</v>
-      </c>
-      <c r="D8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
